--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844721</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844721</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>129844705</v>
       </c>
       <c r="B5" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -907,59 +907,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844721</v>
+        <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>92249</v>
+        <v>83044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528841</v>
+        <v>528939</v>
       </c>
       <c r="R4" t="n">
-        <v>6627526</v>
+        <v>6627368</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,55 +1021,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844705</v>
+        <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>83044</v>
+        <v>92249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528939</v>
+        <v>528841</v>
       </c>
       <c r="R5" t="n">
-        <v>6627368</v>
+        <v>6627526</v>
       </c>
       <c r="S5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -907,55 +907,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844705</v>
+        <v>129844721</v>
       </c>
       <c r="B4" t="n">
-        <v>83047</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528939</v>
+        <v>528841</v>
       </c>
       <c r="R4" t="n">
-        <v>6627368</v>
+        <v>6627526</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,59 +1025,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844721</v>
+        <v>129844705</v>
       </c>
       <c r="B5" t="n">
-        <v>92252</v>
+        <v>83047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528841</v>
+        <v>528939</v>
       </c>
       <c r="R5" t="n">
-        <v>6627526</v>
+        <v>6627368</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -907,59 +907,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844721</v>
+        <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>83047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528841</v>
+        <v>528939</v>
       </c>
       <c r="R4" t="n">
-        <v>6627526</v>
+        <v>6627368</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,55 +1021,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844705</v>
+        <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>83047</v>
+        <v>92252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528939</v>
+        <v>528841</v>
       </c>
       <c r="R5" t="n">
-        <v>6627368</v>
+        <v>6627526</v>
       </c>
       <c r="S5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>83050</v>
+        <v>83051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>129844705</v>
       </c>
       <c r="B4" t="n">
-        <v>83051</v>
+        <v>83057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>129844721</v>
       </c>
       <c r="B5" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844716</v>
       </c>
       <c r="B2" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129844720</v>
       </c>
       <c r="B3" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,55 +907,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844705</v>
+        <v>129844721</v>
       </c>
       <c r="B4" t="n">
-        <v>83065</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528939</v>
+        <v>528841</v>
       </c>
       <c r="R4" t="n">
-        <v>6627368</v>
+        <v>6627526</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,59 +1025,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844721</v>
+        <v>129844705</v>
       </c>
       <c r="B5" t="n">
-        <v>92291</v>
+        <v>83150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528841</v>
+        <v>528939</v>
       </c>
       <c r="R5" t="n">
-        <v>6627526</v>
+        <v>6627368</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
         <v>129844729</v>
       </c>
       <c r="B6" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58355-2025 artfynd.xlsx
+++ b/artfynd/A 58355-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129844716</v>
+        <v>6989777</v>
       </c>
       <c r="B2" t="n">
-        <v>91661</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,44 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda Jorden, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528939</v>
+        <v>528872</v>
       </c>
       <c r="R2" t="n">
-        <v>6627368</v>
+        <v>6627389</v>
       </c>
       <c r="S2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2013-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,75 +756,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Frisk - fuktig barrblandskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mårten Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mårten Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844720</v>
+        <v>6989779</v>
       </c>
       <c r="B3" t="n">
-        <v>92291</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan, Vstm</t>
+          <t>Röda Jorden, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528815</v>
+        <v>528861</v>
       </c>
       <c r="R3" t="n">
-        <v>6627556</v>
+        <v>6627399</v>
       </c>
       <c r="S3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2013-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:11</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,26 +858,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Frisk - fuktig barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mårten Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mårten Berglind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844705</v>
+        <v>129844729</v>
       </c>
       <c r="B4" t="n">
-        <v>83065</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,30 +890,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528939</v>
+        <v>528918</v>
       </c>
       <c r="R4" t="n">
-        <v>6627368</v>
+        <v>6627407</v>
       </c>
       <c r="S4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +971,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,59 +998,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129844721</v>
+        <v>129844705</v>
       </c>
       <c r="B5" t="n">
-        <v>92291</v>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röda jorden, Riddarhyttan , Vstm</t>
+          <t>Röda jorden, Riddarhyttan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528841</v>
+        <v>528939</v>
       </c>
       <c r="R5" t="n">
-        <v>6627526</v>
+        <v>6627368</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,46 +1112,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129844729</v>
+        <v>129844720</v>
       </c>
       <c r="B6" t="n">
-        <v>97079</v>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528918</v>
+        <v>528815</v>
       </c>
       <c r="R6" t="n">
-        <v>6627407</v>
+        <v>6627556</v>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,6 +1227,124 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129844721</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92564</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528841</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6627526</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
